--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R11" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,16 +1739,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1766,7 +1761,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R12" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364504</v>
+        <v>131364490</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626492</v>
+        <v>626705</v>
       </c>
       <c r="R2" t="n">
-        <v>6996470</v>
+        <v>6996447</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364490</v>
+        <v>131364505</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,42 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626705</v>
+        <v>626342</v>
       </c>
       <c r="R3" t="n">
-        <v>6996447</v>
+        <v>6996608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R4" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>131364475</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>131364470</v>
       </c>
       <c r="B7" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364479</v>
+        <v>131364482</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626431</v>
+        <v>626675</v>
       </c>
       <c r="R8" t="n">
-        <v>6996531</v>
+        <v>6996443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364482</v>
+        <v>131364500</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,42 +1422,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626675</v>
+        <v>626487</v>
       </c>
       <c r="R9" t="n">
-        <v>6996443</v>
+        <v>6996447</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1486,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364500</v>
+        <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1524,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626487</v>
+        <v>626431</v>
       </c>
       <c r="R10" t="n">
-        <v>6996447</v>
+        <v>6996531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
         <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131364497</v>
       </c>
       <c r="B15" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>131364488</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>131364493</v>
       </c>
       <c r="B17" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>131364496</v>
       </c>
       <c r="B18" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>131364492</v>
       </c>
       <c r="B19" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364509</v>
+        <v>131364506</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,22 +2614,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626514</v>
+        <v>626636</v>
       </c>
       <c r="R20" t="n">
-        <v>6996422</v>
+        <v>6996473</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2663,7 +2660,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2672,7 +2669,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2691,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2720,19 +2716,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R21" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2766,7 +2765,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,6 +2774,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364478</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,54 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626721</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996435</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2861,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B23" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,37 +2901,54 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R23" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,14 +2978,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,24 +2999,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3041,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364484</v>
+        <v>131364494</v>
       </c>
       <c r="B24" t="n">
-        <v>91835</v>
+        <v>80353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,34 +3028,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626475</v>
+        <v>626292</v>
       </c>
       <c r="R24" t="n">
-        <v>6996475</v>
+        <v>6996716</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,14 +3093,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364469</v>
+        <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626331</v>
+        <v>626684</v>
       </c>
       <c r="R27" t="n">
-        <v>6996760</v>
+        <v>6996454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131364465</v>
+        <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626312</v>
+        <v>626331</v>
       </c>
       <c r="R28" t="n">
-        <v>6996651</v>
+        <v>6996760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R29" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>131364480</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>131364466</v>
       </c>
       <c r="B32" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>131364485</v>
       </c>
       <c r="B33" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364476</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,31 +4175,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626499</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996587</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4247,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,8 +4251,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4274,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364471</v>
+        <v>131364476</v>
       </c>
       <c r="B36" t="n">
-        <v>91814</v>
+        <v>57886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4285,34 +4296,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626744</v>
+        <v>626499</v>
       </c>
       <c r="R36" t="n">
-        <v>6996412</v>
+        <v>6996587</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,6 +4364,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,7 +4398,7 @@
         <v>131364498</v>
       </c>
       <c r="B37" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4492,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>91816</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,40 +4527,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R38" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4568,35 +4589,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4616,7 +4616,7 @@
         <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131364490</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131364505</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131364504</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131364475</v>
+        <v>131364470</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>91817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626332</v>
+        <v>626706</v>
       </c>
       <c r="R6" t="n">
-        <v>6996641</v>
+        <v>6996440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1165,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131364470</v>
+        <v>131364475</v>
       </c>
       <c r="B7" t="n">
-        <v>91816</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626706</v>
+        <v>626332</v>
       </c>
       <c r="R7" t="n">
-        <v>6996440</v>
+        <v>6996641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364482</v>
+        <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,42 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626675</v>
+        <v>626487</v>
       </c>
       <c r="R8" t="n">
-        <v>6996443</v>
+        <v>6996447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1376,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364500</v>
+        <v>131364482</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,34 +1414,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626487</v>
+        <v>626675</v>
       </c>
       <c r="R9" t="n">
-        <v>6996447</v>
+        <v>6996443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
         <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R11" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,6 +1702,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,16 +1744,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1761,7 +1766,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1771,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R12" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1849,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R13" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,8 +1925,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1940,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,42 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R14" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B15" t="n">
-        <v>80353</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,26 +2072,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2083,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R15" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,35 +2142,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>131364488</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>131364493</v>
       </c>
       <c r="B17" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>80353</v>
+        <v>92276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,21 +2453,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2484,48 +2469,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B19" t="n">
-        <v>92275</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R19" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,13 +2542,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,19 +2600,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R20" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2660,7 +2649,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2669,6 +2658,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2687,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,21 +2688,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,13 +2715,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,11 +2751,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364484</v>
+        <v>131364494</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>80354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,34 +2804,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626475</v>
+        <v>626292</v>
       </c>
       <c r="R22" t="n">
-        <v>6996475</v>
+        <v>6996716</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,14 +2869,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2893,7 +2917,7 @@
         <v>131364478</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B24" t="n">
-        <v>80353</v>
+        <v>91838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,37 +3052,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R24" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,35 +3114,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364480</v>
+        <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>91817</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,42 +3757,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626363</v>
+        <v>626481</v>
       </c>
       <c r="R31" t="n">
-        <v>6996784</v>
+        <v>6996600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,11 +3817,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,45 +3843,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364466</v>
+        <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91816</v>
+        <v>91828</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626481</v>
+        <v>626311</v>
       </c>
       <c r="R32" t="n">
-        <v>6996600</v>
+        <v>6996750</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,6 +3925,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3953,37 +3944,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364485</v>
+        <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3991,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626311</v>
+        <v>626363</v>
       </c>
       <c r="R33" t="n">
-        <v>6996750</v>
+        <v>6996784</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,13 +4025,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>91817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,40 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R35" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4240,35 +4237,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4288,7 +4264,7 @@
         <v>131364476</v>
       </c>
       <c r="B36" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4374,7 @@
         <v>131364498</v>
       </c>
       <c r="B37" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B38" t="n">
-        <v>91816</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4527,37 +4503,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R38" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4589,14 +4568,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4616,7 +4616,7 @@
         <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364490</v>
+        <v>131364505</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626705</v>
+        <v>626342</v>
       </c>
       <c r="R2" t="n">
-        <v>6996447</v>
+        <v>6996608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B3" t="n">
         <v>79249</v>
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R3" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364504</v>
+        <v>131364490</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626492</v>
+        <v>626705</v>
       </c>
       <c r="R4" t="n">
-        <v>6996470</v>
+        <v>6996447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,11 +958,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R11" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,16 +1739,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1766,7 +1761,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R12" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364497</v>
+        <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,37 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626310</v>
+        <v>626550</v>
       </c>
       <c r="R13" t="n">
-        <v>6996671</v>
+        <v>6996438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växande på tre aspträd i närområdet</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,24 +1922,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1959,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1951,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R14" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2018,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2043,8 +2027,24 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2368,48 +2368,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B18" t="n">
-        <v>92276</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,13 +2441,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2469,45 +2470,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364506</v>
+        <v>131364492</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>92276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626636</v>
+        <v>626333</v>
       </c>
       <c r="R19" t="n">
-        <v>6996473</v>
+        <v>6996777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,17 +2546,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R20" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,11 +2645,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2661,6 +2656,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2677,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364496</v>
+        <v>131364509</v>
       </c>
       <c r="B21" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,21 +2698,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,13 +2725,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626311</v>
+        <v>626514</v>
       </c>
       <c r="R21" t="n">
-        <v>6996692</v>
+        <v>6996422</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2751,6 +2761,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,21 +2777,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>80354</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,37 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,35 +2866,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2914,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,54 +2901,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R23" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,19 +2961,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,8 +2977,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3041,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,34 +3022,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R24" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,9 +3099,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3358,7 +3358,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B27" t="n">
         <v>91817</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R27" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364465</v>
+        <v>131364467</v>
       </c>
       <c r="B29" t="n">
         <v>91817</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626312</v>
+        <v>626684</v>
       </c>
       <c r="R29" t="n">
-        <v>6996651</v>
+        <v>6996454</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,37 +4175,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,14 +4240,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4261,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B36" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,31 +4296,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4304,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R36" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4344,7 +4363,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4353,8 +4372,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4371,10 +4406,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364498</v>
+        <v>131364471</v>
       </c>
       <c r="B37" t="n">
-        <v>80354</v>
+        <v>91817</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4382,37 +4417,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626471</v>
+        <v>626744</v>
       </c>
       <c r="R37" t="n">
-        <v>6996618</v>
+        <v>6996412</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,35 +4479,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4492,10 +4503,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364501</v>
+        <v>131364476</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,26 +4514,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,13 +4546,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626458</v>
+        <v>626499</v>
       </c>
       <c r="R38" t="n">
-        <v>6996478</v>
+        <v>6996587</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4579,24 +4595,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364507</v>
+        <v>131364487</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1849,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626550</v>
+        <v>626322</v>
       </c>
       <c r="R13" t="n">
-        <v>6996438</v>
+        <v>6996755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,11 +1917,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,42 +2075,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R15" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,6 +2135,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>92115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,42 +2177,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R16" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>92115</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,34 +2274,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R17" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,45 +2368,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364506</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>92276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626636</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996473</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,17 +2444,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2470,48 +2469,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B19" t="n">
-        <v>92276</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R19" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,13 +2542,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364496</v>
+        <v>131364509</v>
       </c>
       <c r="B20" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626311</v>
+        <v>626514</v>
       </c>
       <c r="R20" t="n">
-        <v>6996692</v>
+        <v>6996422</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,6 +2645,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2656,21 +2661,6 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2687,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,21 +2688,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,13 +2715,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,11 +2751,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B23" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,37 +2901,54 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R23" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,14 +2978,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2977,24 +2999,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3011,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,54 +3028,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R24" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,19 +3088,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,8 +3104,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3358,7 +3358,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364465</v>
+        <v>131364467</v>
       </c>
       <c r="B27" t="n">
         <v>91817</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626312</v>
+        <v>626684</v>
       </c>
       <c r="R27" t="n">
-        <v>6996651</v>
+        <v>6996454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B29" t="n">
         <v>91817</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R29" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,40 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R35" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4240,35 +4237,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4285,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364498</v>
+        <v>131364501</v>
       </c>
       <c r="B36" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,21 +4272,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,13 +4299,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626471</v>
+        <v>626458</v>
       </c>
       <c r="R36" t="n">
-        <v>6996618</v>
+        <v>6996478</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4363,7 +4339,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,17 +4354,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4406,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364471</v>
+        <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,34 +4393,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626744</v>
+        <v>626499</v>
       </c>
       <c r="R37" t="n">
-        <v>6996412</v>
+        <v>6996587</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,6 +4461,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4503,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,31 +4503,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4546,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R38" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,8 +4579,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,34 +4624,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R39" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,42 +4729,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R40" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131364505</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131364504</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131364490</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>131364470</v>
       </c>
       <c r="B6" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131364475</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>131364482</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,42 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R13" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,6 +1909,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,7 +1943,7 @@
         <v>131364497</v>
       </c>
       <c r="B14" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364507</v>
+        <v>131364487</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,34 +2072,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626550</v>
+        <v>626322</v>
       </c>
       <c r="R15" t="n">
-        <v>6996438</v>
+        <v>6996755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,11 +2140,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,7 +2169,7 @@
         <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>92276</v>
+        <v>92277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>131364506</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>131364509</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,34 +2804,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R22" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,9 +2881,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,54 +2931,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R23" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,19 +2991,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,8 +3007,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3017,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B24" t="n">
-        <v>80354</v>
+        <v>91839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,37 +3052,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R24" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,35 +3114,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>131364501</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,31 +4393,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R37" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,7 +4460,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4474,8 +4469,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4492,10 +4503,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364498</v>
+        <v>131364476</v>
       </c>
       <c r="B38" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,26 +4514,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626471</v>
+        <v>626499</v>
       </c>
       <c r="R38" t="n">
-        <v>6996618</v>
+        <v>6996587</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4579,24 +4595,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,42 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R39" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4729,34 +4726,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R40" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B2" t="n">
         <v>79250</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R2" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364504</v>
+        <v>131364505</v>
       </c>
       <c r="B3" t="n">
         <v>79250</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626492</v>
+        <v>626342</v>
       </c>
       <c r="R3" t="n">
-        <v>6996470</v>
+        <v>6996608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1849,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R13" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,8 +1925,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1940,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>80355</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,26 +1970,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1978,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R14" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,35 +2040,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,42 +2075,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R15" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,6 +2135,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B16" t="n">
-        <v>92116</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,34 +2177,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R16" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>92116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,42 +2282,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R17" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364509</v>
       </c>
       <c r="B18" t="n">
-        <v>92277</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626514</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996422</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,6 +2442,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,13 +2614,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R20" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,11 +2650,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2661,6 +2661,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2677,32 +2692,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B21" t="n">
-        <v>80355</v>
+        <v>92277</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R21" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,21 +2777,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364478</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>91839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,54 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626721</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996435</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2861,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>91839</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,34 +3022,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R24" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,9 +3099,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364471</v>
+        <v>131364476</v>
       </c>
       <c r="B35" t="n">
-        <v>91818</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,34 +4175,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626744</v>
+        <v>626499</v>
       </c>
       <c r="R35" t="n">
-        <v>6996412</v>
+        <v>6996587</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4235,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4261,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,40 +4285,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R36" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4337,35 +4347,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4382,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364498</v>
+        <v>131364501</v>
       </c>
       <c r="B37" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,21 +4382,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,13 +4409,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626471</v>
+        <v>626458</v>
       </c>
       <c r="R37" t="n">
-        <v>6996618</v>
+        <v>6996478</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4460,7 +4449,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,17 +4464,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4503,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B38" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,31 +4503,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4546,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R38" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,8 +4579,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364509</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>92277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626514</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996422</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,11 +2442,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B19" t="n">
         <v>79250</v>
@@ -2503,19 +2498,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R19" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,7 +2547,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,6 +2556,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2576,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364496</v>
+        <v>131364506</v>
       </c>
       <c r="B20" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,37 +2586,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626311</v>
+        <v>626636</v>
       </c>
       <c r="R20" t="n">
-        <v>6996692</v>
+        <v>6996473</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,30 +2648,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2692,32 +2677,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>92277</v>
+        <v>80355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,34 +4624,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R39" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,42 +4729,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R40" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364504</v>
+        <v>131364490</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626492</v>
+        <v>626705</v>
       </c>
       <c r="R2" t="n">
-        <v>6996470</v>
+        <v>6996447</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +783,7 @@
         <v>131364505</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364490</v>
+        <v>131364504</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626705</v>
+        <v>626492</v>
       </c>
       <c r="R4" t="n">
-        <v>6996447</v>
+        <v>6996470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,6 +953,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>131364470</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131364475</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>131364482</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>131364497</v>
       </c>
       <c r="B13" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>131364507</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>92119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,42 +2177,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R16" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>92116</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,34 +2274,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R17" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
         <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364509</v>
+        <v>131364506</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,22 +2498,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626514</v>
+        <v>626636</v>
       </c>
       <c r="R19" t="n">
-        <v>6996422</v>
+        <v>6996473</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2547,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2553,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2575,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,19 +2600,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R20" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2650,7 +2649,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,6 +2658,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364466</v>
+        <v>131364480</v>
       </c>
       <c r="B31" t="n">
-        <v>91818</v>
+        <v>57891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,34 +3757,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626481</v>
+        <v>626363</v>
       </c>
       <c r="R31" t="n">
-        <v>6996600</v>
+        <v>6996784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,6 +3825,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3843,48 +3856,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364485</v>
+        <v>131364466</v>
       </c>
       <c r="B32" t="n">
-        <v>91829</v>
+        <v>91821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626311</v>
+        <v>626481</v>
       </c>
       <c r="R32" t="n">
-        <v>6996750</v>
+        <v>6996600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3935,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3944,42 +3953,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364480</v>
+        <v>131364485</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>91832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3987,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626363</v>
+        <v>626311</v>
       </c>
       <c r="R33" t="n">
-        <v>6996784</v>
+        <v>6996750</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,17 +4029,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364476</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,31 +4175,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626499</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996587</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4247,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,8 +4251,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4274,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364471</v>
+        <v>131364498</v>
       </c>
       <c r="B36" t="n">
-        <v>91818</v>
+        <v>80358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4285,34 +4296,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626744</v>
+        <v>626471</v>
       </c>
       <c r="R36" t="n">
-        <v>6996412</v>
+        <v>6996618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4347,14 +4361,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4371,10 +4406,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364501</v>
+        <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4382,26 +4417,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4409,13 +4449,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626458</v>
+        <v>626499</v>
       </c>
       <c r="R37" t="n">
-        <v>6996478</v>
+        <v>6996587</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4449,7 +4489,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4458,24 +4498,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4492,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364498</v>
+        <v>131364471</v>
       </c>
       <c r="B38" t="n">
-        <v>80355</v>
+        <v>91821</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,37 +4527,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626471</v>
+        <v>626744</v>
       </c>
       <c r="R38" t="n">
-        <v>6996618</v>
+        <v>6996412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4568,35 +4589,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,42 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R39" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4729,34 +4726,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R40" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364490</v>
+        <v>131364505</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626705</v>
+        <v>626342</v>
       </c>
       <c r="R2" t="n">
-        <v>6996447</v>
+        <v>6996608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R3" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364504</v>
+        <v>131364490</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626492</v>
+        <v>626705</v>
       </c>
       <c r="R4" t="n">
-        <v>6996470</v>
+        <v>6996447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,11 +958,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131364470</v>
+        <v>131364475</v>
       </c>
       <c r="B6" t="n">
-        <v>91821</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1105,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626706</v>
+        <v>626332</v>
       </c>
       <c r="R6" t="n">
-        <v>6996440</v>
+        <v>6996641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131364475</v>
+        <v>131364470</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>91822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,42 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626332</v>
+        <v>626706</v>
       </c>
       <c r="R7" t="n">
-        <v>6996641</v>
+        <v>6996440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364500</v>
+        <v>131364482</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,34 +1312,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626487</v>
+        <v>626675</v>
       </c>
       <c r="R8" t="n">
-        <v>6996447</v>
+        <v>6996443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,7 +1384,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364482</v>
+        <v>131364479</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626675</v>
+        <v>626431</v>
       </c>
       <c r="R9" t="n">
-        <v>6996443</v>
+        <v>6996531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364479</v>
+        <v>131364500</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,42 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626431</v>
+        <v>626487</v>
       </c>
       <c r="R10" t="n">
-        <v>6996531</v>
+        <v>6996447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R11" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,6 +1702,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,16 +1744,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1761,7 +1766,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1771,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R12" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364497</v>
+        <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,37 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626310</v>
+        <v>626550</v>
       </c>
       <c r="R13" t="n">
-        <v>6996671</v>
+        <v>6996438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växande på tre aspträd i närområdet</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,24 +1922,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1962,7 +1943,7 @@
         <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>80359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,34 +2056,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R15" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2123,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,8 +2132,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,48 +2368,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B18" t="n">
-        <v>92280</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,13 +2441,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2469,45 +2470,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364506</v>
+        <v>131364492</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>92281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626636</v>
+        <v>626333</v>
       </c>
       <c r="R19" t="n">
-        <v>6996473</v>
+        <v>6996777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,17 +2546,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>131364509</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B23" t="n">
-        <v>80358</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,37 +2901,54 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R23" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,14 +2978,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2977,24 +2999,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3011,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>80359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,54 +3028,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R24" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,19 +3088,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,8 +3104,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B27" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R27" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364465</v>
+        <v>131364467</v>
       </c>
       <c r="B29" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626312</v>
+        <v>626684</v>
       </c>
       <c r="R29" t="n">
-        <v>6996651</v>
+        <v>6996454</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364480</v>
+        <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>57891</v>
+        <v>91822</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,42 +3757,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626363</v>
+        <v>626481</v>
       </c>
       <c r="R31" t="n">
-        <v>6996784</v>
+        <v>6996600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,11 +3817,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,45 +3843,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364466</v>
+        <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91821</v>
+        <v>91833</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626481</v>
+        <v>626311</v>
       </c>
       <c r="R32" t="n">
-        <v>6996600</v>
+        <v>6996750</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,6 +3925,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3953,37 +3944,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364485</v>
+        <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>91832</v>
+        <v>57892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3991,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626311</v>
+        <v>626363</v>
       </c>
       <c r="R33" t="n">
-        <v>6996750</v>
+        <v>6996784</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,13 +4025,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>91822</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,40 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R35" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4240,35 +4237,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4285,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364498</v>
+        <v>131364501</v>
       </c>
       <c r="B36" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,21 +4272,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,13 +4299,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626471</v>
+        <v>626458</v>
       </c>
       <c r="R36" t="n">
-        <v>6996618</v>
+        <v>6996478</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4363,7 +4339,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,17 +4354,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4409,7 +4385,7 @@
         <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364471</v>
+        <v>131364498</v>
       </c>
       <c r="B38" t="n">
-        <v>91821</v>
+        <v>80359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4527,34 +4503,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626744</v>
+        <v>626471</v>
       </c>
       <c r="R38" t="n">
-        <v>6996412</v>
+        <v>6996618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,14 +4568,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,34 +4624,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R39" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,42 +4729,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R40" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131364475</v>
+        <v>131364470</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>91822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626332</v>
+        <v>626706</v>
       </c>
       <c r="R6" t="n">
-        <v>6996641</v>
+        <v>6996440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1165,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131364470</v>
+        <v>131364475</v>
       </c>
       <c r="B7" t="n">
-        <v>91822</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626706</v>
+        <v>626332</v>
       </c>
       <c r="R7" t="n">
-        <v>6996440</v>
+        <v>6996641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2368,45 +2368,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364506</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>92281</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626636</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996473</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,17 +2444,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2470,32 +2469,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364492</v>
+        <v>131364509</v>
       </c>
       <c r="B19" t="n">
-        <v>92281</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2508,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626333</v>
+        <v>626514</v>
       </c>
       <c r="R19" t="n">
-        <v>6996777</v>
+        <v>6996422</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,6 +2543,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>80359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,21 +2586,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,13 +2613,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R20" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,11 +2649,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2661,6 +2660,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2677,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364496</v>
+        <v>131364506</v>
       </c>
       <c r="B21" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,37 +2702,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626311</v>
+        <v>626636</v>
       </c>
       <c r="R21" t="n">
-        <v>6996692</v>
+        <v>6996473</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,30 +2764,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>91822</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,37 +4175,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,14 +4240,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4261,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364501</v>
+        <v>131364476</v>
       </c>
       <c r="B36" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,26 +4296,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4299,13 +4328,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626458</v>
+        <v>626499</v>
       </c>
       <c r="R36" t="n">
-        <v>6996478</v>
+        <v>6996587</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4339,7 +4368,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4348,24 +4377,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4382,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364476</v>
+        <v>131364471</v>
       </c>
       <c r="B37" t="n">
-        <v>57892</v>
+        <v>91822</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,42 +4406,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626499</v>
+        <v>626744</v>
       </c>
       <c r="R37" t="n">
-        <v>6996587</v>
+        <v>6996412</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4461,11 +4466,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131364505</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131364504</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131364490</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>131364470</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131364475</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364482</v>
+        <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,42 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626675</v>
+        <v>626487</v>
       </c>
       <c r="R8" t="n">
-        <v>6996443</v>
+        <v>6996447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1376,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364479</v>
+        <v>131364482</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626431</v>
+        <v>626675</v>
       </c>
       <c r="R9" t="n">
-        <v>6996531</v>
+        <v>6996443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364500</v>
+        <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1524,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626487</v>
+        <v>626431</v>
       </c>
       <c r="R10" t="n">
-        <v>6996447</v>
+        <v>6996531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R11" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,16 +1739,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1766,7 +1761,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R12" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1841,7 @@
         <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364487</v>
+        <v>131364497</v>
       </c>
       <c r="B14" t="n">
-        <v>57889</v>
+        <v>80365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,31 +1951,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1983,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626322</v>
+        <v>626310</v>
       </c>
       <c r="R14" t="n">
-        <v>6996755</v>
+        <v>6996671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,14 +2016,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växande på tre aspträd i närområdet</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2045,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B15" t="n">
-        <v>80359</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,26 +2072,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2083,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R15" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,35 +2142,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B18" t="n">
-        <v>92281</v>
+        <v>80365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2453,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2469,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364509</v>
+        <v>131364492</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2507,13 +2522,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626514</v>
+        <v>626333</v>
       </c>
       <c r="R19" t="n">
-        <v>6996422</v>
+        <v>6996777</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,11 +2558,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364496</v>
+        <v>131364506</v>
       </c>
       <c r="B20" t="n">
-        <v>80359</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2586,37 +2596,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626311</v>
+        <v>626636</v>
       </c>
       <c r="R20" t="n">
-        <v>6996692</v>
+        <v>6996473</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,30 +2658,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2691,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2720,19 +2716,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R21" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2766,7 +2765,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,6 +2774,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B22" t="n">
-        <v>91843</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,34 +2804,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R22" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,9 +2881,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364478</v>
+        <v>131364484</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>91849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,54 +2931,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626721</v>
+        <v>626475</v>
       </c>
       <c r="R23" t="n">
-        <v>6996435</v>
+        <v>6996475</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,19 +2988,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3020,7 +3020,7 @@
         <v>131364494</v>
       </c>
       <c r="B24" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364465</v>
+        <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626312</v>
+        <v>626684</v>
       </c>
       <c r="R27" t="n">
-        <v>6996651</v>
+        <v>6996454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R29" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91833</v>
+        <v>91839</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B36" t="n">
-        <v>57892</v>
+        <v>80365</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,31 +4296,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4328,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R36" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4363,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4377,8 +4372,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4398,7 +4409,7 @@
         <v>131364471</v>
       </c>
       <c r="B37" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4492,10 +4503,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364498</v>
+        <v>131364476</v>
       </c>
       <c r="B38" t="n">
-        <v>80359</v>
+        <v>57898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,26 +4514,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626471</v>
+        <v>626499</v>
       </c>
       <c r="R38" t="n">
-        <v>6996618</v>
+        <v>6996587</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4579,24 +4595,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>57889</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,42 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R39" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>79254</v>
+        <v>57895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4729,34 +4726,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R40" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364500</v>
+        <v>131364482</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,34 +1312,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626487</v>
+        <v>626675</v>
       </c>
       <c r="R8" t="n">
-        <v>6996447</v>
+        <v>6996443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,7 +1384,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,7 +1411,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364482</v>
+        <v>131364479</v>
       </c>
       <c r="B9" t="n">
         <v>57898</v>
@@ -1446,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626675</v>
+        <v>626431</v>
       </c>
       <c r="R9" t="n">
-        <v>6996443</v>
+        <v>6996531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364479</v>
+        <v>131364500</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,42 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626431</v>
+        <v>626487</v>
       </c>
       <c r="R10" t="n">
-        <v>6996531</v>
+        <v>6996447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1849,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R13" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,8 +1925,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1940,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>80365</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,26 +1970,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1978,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R14" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,35 +2040,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2061,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,42 +2075,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R15" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,6 +2135,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,21 +2453,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2484,48 +2469,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B19" t="n">
-        <v>92287</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R19" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,13 +2542,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B20" t="n">
         <v>79260</v>
@@ -2614,19 +2600,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R20" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2660,7 +2649,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2669,6 +2658,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2687,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,21 +2688,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,13 +2715,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,11 +2751,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364478</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>91849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,54 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626721</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996435</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2861,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364484</v>
+        <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>91849</v>
+        <v>80365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,34 +2901,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626475</v>
+        <v>626292</v>
       </c>
       <c r="R23" t="n">
-        <v>6996475</v>
+        <v>6996716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,14 +2966,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3017,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,37 +3022,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R24" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,14 +3099,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3104,24 +3120,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,40 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R35" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4240,35 +4237,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4406,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364471</v>
+        <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>91828</v>
+        <v>57898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,34 +4393,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626744</v>
+        <v>626499</v>
       </c>
       <c r="R37" t="n">
-        <v>6996412</v>
+        <v>6996587</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,6 +4461,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4503,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364476</v>
+        <v>131364501</v>
       </c>
       <c r="B38" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,31 +4503,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4546,13 +4530,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626499</v>
+        <v>626458</v>
       </c>
       <c r="R38" t="n">
-        <v>6996587</v>
+        <v>6996478</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4586,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,8 +4579,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364505</v>
+        <v>131364490</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626342</v>
+        <v>626705</v>
       </c>
       <c r="R2" t="n">
-        <v>6996608</v>
+        <v>6996447</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364504</v>
+        <v>131364505</v>
       </c>
       <c r="B3" t="n">
         <v>79260</v>
@@ -812,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626492</v>
+        <v>626342</v>
       </c>
       <c r="R3" t="n">
-        <v>6996470</v>
+        <v>6996608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364490</v>
+        <v>131364504</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626705</v>
+        <v>626492</v>
       </c>
       <c r="R4" t="n">
-        <v>6996447</v>
+        <v>6996470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,6 +953,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364482</v>
+        <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,42 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626675</v>
+        <v>626487</v>
       </c>
       <c r="R8" t="n">
-        <v>6996443</v>
+        <v>6996447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1376,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364479</v>
+        <v>131364482</v>
       </c>
       <c r="B9" t="n">
         <v>57898</v>
@@ -1454,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626431</v>
+        <v>626675</v>
       </c>
       <c r="R9" t="n">
-        <v>6996531</v>
+        <v>6996443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364500</v>
+        <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1524,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626487</v>
+        <v>626431</v>
       </c>
       <c r="R10" t="n">
-        <v>6996447</v>
+        <v>6996531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R11" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,6 +1702,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,16 +1744,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1761,7 +1766,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1771,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R12" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364497</v>
+        <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,37 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626310</v>
+        <v>626550</v>
       </c>
       <c r="R13" t="n">
-        <v>6996671</v>
+        <v>6996438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växande på tre aspträd i närområdet</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,24 +1922,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2064,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,34 +2056,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R15" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2123,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,8 +2132,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B23" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,37 +2901,54 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R23" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,14 +2978,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2977,24 +2999,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3011,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,54 +3028,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R24" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,19 +3088,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,8 +3104,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,37 +4175,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,14 +4240,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4261,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364498</v>
+        <v>131364476</v>
       </c>
       <c r="B36" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,26 +4296,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4299,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626471</v>
+        <v>626499</v>
       </c>
       <c r="R36" t="n">
-        <v>6996618</v>
+        <v>6996587</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4339,7 +4368,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4348,24 +4377,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4382,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,31 +4406,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R37" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,7 +4473,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4474,8 +4482,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4492,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,40 +4527,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R38" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4568,35 +4589,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R11" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,16 +1739,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1766,7 +1761,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R12" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364507</v>
+        <v>131364487</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1849,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626550</v>
+        <v>626322</v>
       </c>
       <c r="R13" t="n">
-        <v>6996438</v>
+        <v>6996755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,11 +1917,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364487</v>
+        <v>131364497</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>80365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,31 +1954,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1983,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626322</v>
+        <v>626310</v>
       </c>
       <c r="R14" t="n">
-        <v>6996755</v>
+        <v>6996671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,14 +2019,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växande på tre aspträd i närområdet</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2045,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364497</v>
+        <v>131364507</v>
       </c>
       <c r="B15" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,37 +2075,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626310</v>
+        <v>626550</v>
       </c>
       <c r="R15" t="n">
-        <v>6996671</v>
+        <v>6996438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2139,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växande på tre aspträd i närområdet</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,24 +2148,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B16" t="n">
-        <v>92126</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,34 +2177,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R16" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B17" t="n">
-        <v>57895</v>
+        <v>92126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,42 +2282,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R17" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364487</v>
+        <v>131364497</v>
       </c>
       <c r="B13" t="n">
-        <v>57895</v>
+        <v>80365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,31 +1849,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1881,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626322</v>
+        <v>626310</v>
       </c>
       <c r="R13" t="n">
-        <v>6996755</v>
+        <v>6996671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,14 +1914,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växande på tre aspträd i närområdet</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1943,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>80365</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,26 +1970,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R14" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,35 +2040,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>92127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,42 +2177,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R16" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>92126</v>
+        <v>57895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,34 +2274,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R17" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>80365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2453,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2677,32 +2692,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B21" t="n">
-        <v>80365</v>
+        <v>92288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R21" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,21 +2777,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364484</v>
+        <v>131364494</v>
       </c>
       <c r="B22" t="n">
-        <v>91849</v>
+        <v>80365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,34 +2804,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626475</v>
+        <v>626292</v>
       </c>
       <c r="R22" t="n">
-        <v>6996475</v>
+        <v>6996716</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,14 +2869,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3017,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B24" t="n">
-        <v>80365</v>
+        <v>91849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,37 +3052,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R24" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,35 +3114,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364501</v>
+        <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,40 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626458</v>
+        <v>626744</v>
       </c>
       <c r="R35" t="n">
-        <v>6996478</v>
+        <v>6996412</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4240,35 +4237,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4285,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B36" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,31 +4272,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4328,10 +4299,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R36" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4339,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4377,8 +4348,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4395,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364498</v>
+        <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4406,26 +4393,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4433,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626471</v>
+        <v>626499</v>
       </c>
       <c r="R37" t="n">
-        <v>6996618</v>
+        <v>6996587</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4473,7 +4465,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4482,24 +4474,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4516,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B38" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4527,37 +4503,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R38" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4589,14 +4568,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,34 +4624,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R39" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,42 +4729,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R40" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131364490</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R3" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364504</v>
+        <v>131364505</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626492</v>
+        <v>626342</v>
       </c>
       <c r="R4" t="n">
-        <v>6996470</v>
+        <v>6996608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131364470</v>
+        <v>131364475</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1105,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626706</v>
+        <v>626332</v>
       </c>
       <c r="R6" t="n">
-        <v>6996440</v>
+        <v>6996641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131364475</v>
+        <v>131364470</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>91829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,42 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626332</v>
+        <v>626706</v>
       </c>
       <c r="R7" t="n">
-        <v>6996641</v>
+        <v>6996440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364500</v>
+        <v>131364482</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,34 +1312,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626487</v>
+        <v>626675</v>
       </c>
       <c r="R8" t="n">
-        <v>6996447</v>
+        <v>6996443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,7 +1384,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364482</v>
+        <v>131364479</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626675</v>
+        <v>626431</v>
       </c>
       <c r="R9" t="n">
-        <v>6996443</v>
+        <v>6996531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364479</v>
+        <v>131364500</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,42 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626431</v>
+        <v>626487</v>
       </c>
       <c r="R10" t="n">
-        <v>6996531</v>
+        <v>6996447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
         <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364497</v>
+        <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,37 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626310</v>
+        <v>626550</v>
       </c>
       <c r="R13" t="n">
-        <v>6996671</v>
+        <v>6996438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1913,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växande på tre aspträd i närområdet</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,24 +1922,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1962,7 +1943,7 @@
         <v>131364487</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,34 +2056,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R15" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2123,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,8 +2132,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364496</v>
+        <v>131364509</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626311</v>
+        <v>626514</v>
       </c>
       <c r="R18" t="n">
-        <v>6996692</v>
+        <v>6996422</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,6 +2442,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2453,21 +2458,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2487,7 +2477,7 @@
         <v>131364506</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,32 +2576,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364509</v>
+        <v>131364492</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>92289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,13 +2614,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626514</v>
+        <v>626333</v>
       </c>
       <c r="R20" t="n">
-        <v>6996422</v>
+        <v>6996777</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2660,11 +2650,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2692,32 +2677,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>92288</v>
+        <v>80366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>80365</v>
+        <v>91850</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,37 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,35 +2866,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2914,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,54 +2901,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R23" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,19 +2961,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,8 +2977,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3041,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>91849</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,34 +3022,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R24" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,9 +3099,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364466</v>
+        <v>131364480</v>
       </c>
       <c r="B31" t="n">
-        <v>91828</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,34 +3757,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626481</v>
+        <v>626363</v>
       </c>
       <c r="R31" t="n">
-        <v>6996600</v>
+        <v>6996784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,6 +3825,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3843,48 +3856,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364485</v>
+        <v>131364466</v>
       </c>
       <c r="B32" t="n">
-        <v>91839</v>
+        <v>91829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626311</v>
+        <v>626481</v>
       </c>
       <c r="R32" t="n">
-        <v>6996750</v>
+        <v>6996600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3935,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3944,42 +3953,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364480</v>
+        <v>131364485</v>
       </c>
       <c r="B33" t="n">
-        <v>57898</v>
+        <v>91840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3987,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626363</v>
+        <v>626311</v>
       </c>
       <c r="R33" t="n">
-        <v>6996784</v>
+        <v>6996750</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,17 +4029,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>91828</v>
+        <v>79261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,37 +4175,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,14 +4240,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4261,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364498</v>
+        <v>131364471</v>
       </c>
       <c r="B36" t="n">
-        <v>80365</v>
+        <v>91829</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,37 +4296,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626471</v>
+        <v>626744</v>
       </c>
       <c r="R36" t="n">
-        <v>6996618</v>
+        <v>6996412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,35 +4358,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364476</v>
+        <v>131364498</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,31 +4393,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626499</v>
+        <v>626471</v>
       </c>
       <c r="R37" t="n">
-        <v>6996587</v>
+        <v>6996618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,7 +4460,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4474,8 +4469,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4492,10 +4503,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364501</v>
+        <v>131364476</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,26 +4514,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,13 +4546,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626458</v>
+        <v>626499</v>
       </c>
       <c r="R38" t="n">
-        <v>6996478</v>
+        <v>6996587</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4579,24 +4595,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4616,7 +4616,7 @@
         <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364490</v>
+        <v>131364504</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626705</v>
+        <v>626492</v>
       </c>
       <c r="R2" t="n">
-        <v>6996447</v>
+        <v>6996470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364504</v>
+        <v>131364505</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626492</v>
+        <v>626342</v>
       </c>
       <c r="R3" t="n">
-        <v>6996470</v>
+        <v>6996608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131364505</v>
+        <v>131364490</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626342</v>
+        <v>626705</v>
       </c>
       <c r="R4" t="n">
-        <v>6996608</v>
+        <v>6996447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,11 +958,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131364475</v>
+        <v>131364470</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>91832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626332</v>
+        <v>626706</v>
       </c>
       <c r="R6" t="n">
-        <v>6996641</v>
+        <v>6996440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1165,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131364470</v>
+        <v>131364475</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626706</v>
+        <v>626332</v>
       </c>
       <c r="R7" t="n">
-        <v>6996440</v>
+        <v>6996641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364482</v>
+        <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,42 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626675</v>
+        <v>626487</v>
       </c>
       <c r="R8" t="n">
-        <v>6996443</v>
+        <v>6996447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1376,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364479</v>
+        <v>131364482</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626431</v>
+        <v>626675</v>
       </c>
       <c r="R9" t="n">
-        <v>6996531</v>
+        <v>6996443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364500</v>
+        <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1524,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626487</v>
+        <v>626431</v>
       </c>
       <c r="R10" t="n">
-        <v>6996447</v>
+        <v>6996531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R11" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,6 +1702,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B12" t="n">
         <v>57899</v>
@@ -1739,16 +1744,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1761,7 +1766,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1771,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R12" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,34 +1849,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R13" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,8 +1925,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1940,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,42 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R14" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B15" t="n">
-        <v>80366</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,26 +2072,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2083,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R15" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,35 +2142,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364509</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>92292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626514</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996422</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,11 +2442,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,19 +2498,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R19" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,7 +2547,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,6 +2556,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2576,48 +2575,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B20" t="n">
-        <v>92289</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R20" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,13 +2648,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>131364480</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>131364466</v>
       </c>
       <c r="B32" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>131364485</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364501</v>
+        <v>131364498</v>
       </c>
       <c r="B35" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626458</v>
+        <v>626471</v>
       </c>
       <c r="R35" t="n">
-        <v>6996478</v>
+        <v>6996618</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,17 +4257,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
         <v>131364471</v>
       </c>
       <c r="B36" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364498</v>
+        <v>131364501</v>
       </c>
       <c r="B37" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,13 +4420,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626471</v>
+        <v>626458</v>
       </c>
       <c r="R37" t="n">
-        <v>6996618</v>
+        <v>6996478</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,17 +4475,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
         <v>131364476</v>
       </c>
       <c r="B38" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,42 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R39" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4729,34 +4726,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R40" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364504</v>
+        <v>131364505</v>
       </c>
       <c r="B2" t="n">
         <v>79264</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626492</v>
+        <v>626342</v>
       </c>
       <c r="R2" t="n">
-        <v>6996470</v>
+        <v>6996608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B3" t="n">
         <v>79264</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R3" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,34 +2177,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R16" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>92131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,42 +2282,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R17" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,48 +2368,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B18" t="n">
-        <v>92292</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,13 +2441,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2575,45 +2576,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364506</v>
+        <v>131364492</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>92292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626636</v>
+        <v>626333</v>
       </c>
       <c r="R20" t="n">
-        <v>6996473</v>
+        <v>6996777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,17 +2652,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364480</v>
+        <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,42 +3757,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626363</v>
+        <v>626481</v>
       </c>
       <c r="R31" t="n">
-        <v>6996784</v>
+        <v>6996600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,11 +3817,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,45 +3843,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364466</v>
+        <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91832</v>
+        <v>91843</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626481</v>
+        <v>626311</v>
       </c>
       <c r="R32" t="n">
-        <v>6996600</v>
+        <v>6996750</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,6 +3925,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3953,37 +3944,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364485</v>
+        <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>91843</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3991,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626311</v>
+        <v>626363</v>
       </c>
       <c r="R33" t="n">
-        <v>6996750</v>
+        <v>6996784</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,13 +4025,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364498</v>
+        <v>131364471</v>
       </c>
       <c r="B35" t="n">
-        <v>80369</v>
+        <v>91832</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,37 +4175,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626471</v>
+        <v>626744</v>
       </c>
       <c r="R35" t="n">
-        <v>6996618</v>
+        <v>6996412</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4240,35 +4237,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4285,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364471</v>
+        <v>131364498</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
+        <v>80369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4296,34 +4272,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626744</v>
+        <v>626471</v>
       </c>
       <c r="R36" t="n">
-        <v>6996412</v>
+        <v>6996618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,14 +4337,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364501</v>
+        <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,26 +4393,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4420,13 +4425,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626458</v>
+        <v>626499</v>
       </c>
       <c r="R37" t="n">
-        <v>6996478</v>
+        <v>6996587</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4460,7 +4465,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4469,24 +4474,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4503,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364476</v>
+        <v>131364501</v>
       </c>
       <c r="B38" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,31 +4503,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4546,13 +4530,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626499</v>
+        <v>626458</v>
       </c>
       <c r="R38" t="n">
-        <v>6996587</v>
+        <v>6996478</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4586,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,8 +4579,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131364505</v>
+        <v>131364504</v>
       </c>
       <c r="B2" t="n">
         <v>79264</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626342</v>
+        <v>626492</v>
       </c>
       <c r="R2" t="n">
-        <v>6996608</v>
+        <v>6996470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131364504</v>
+        <v>131364505</v>
       </c>
       <c r="B3" t="n">
         <v>79264</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626492</v>
+        <v>626342</v>
       </c>
       <c r="R3" t="n">
-        <v>6996470</v>
+        <v>6996608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131364470</v>
+        <v>131364475</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1105,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626706</v>
+        <v>626332</v>
       </c>
       <c r="R6" t="n">
-        <v>6996440</v>
+        <v>6996641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131364475</v>
+        <v>131364470</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,42 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626332</v>
+        <v>626706</v>
       </c>
       <c r="R7" t="n">
-        <v>6996641</v>
+        <v>6996440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B13" t="n">
-        <v>80369</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,26 +1849,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1876,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R13" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,35 +1919,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2061,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364487</v>
+        <v>131364497</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,31 +2056,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2104,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626322</v>
+        <v>626310</v>
       </c>
       <c r="R15" t="n">
-        <v>6996755</v>
+        <v>6996671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,14 +2121,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växande på tre aspträd i närområdet</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131364488</v>
+        <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,42 +2177,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626307</v>
+        <v>626706</v>
       </c>
       <c r="R16" t="n">
-        <v>6996716</v>
+        <v>6996438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131364493</v>
+        <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>92131</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,34 +2274,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626706</v>
+        <v>626307</v>
       </c>
       <c r="R17" t="n">
-        <v>6996438</v>
+        <v>6996716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B18" t="n">
         <v>79264</v>
@@ -2397,19 +2397,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R18" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,7 +2446,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2452,6 +2455,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2470,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364509</v>
+        <v>131364506</v>
       </c>
       <c r="B19" t="n">
         <v>79264</v>
@@ -2499,22 +2503,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626514</v>
+        <v>626636</v>
       </c>
       <c r="R19" t="n">
-        <v>6996422</v>
+        <v>6996473</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2548,7 +2549,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2557,7 +2558,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B22" t="n">
-        <v>91853</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,34 +2804,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R22" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,9 +2881,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B23" t="n">
-        <v>80369</v>
+        <v>91853</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,37 +2931,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R23" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,35 +2993,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3011,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,54 +3028,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R24" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,19 +3088,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,8 +3104,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3358,7 +3358,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B27" t="n">
         <v>91832</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R27" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364465</v>
+        <v>131364467</v>
       </c>
       <c r="B29" t="n">
         <v>91832</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626312</v>
+        <v>626684</v>
       </c>
       <c r="R29" t="n">
-        <v>6996651</v>
+        <v>6996454</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364466</v>
+        <v>131364480</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,34 +3757,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626481</v>
+        <v>626363</v>
       </c>
       <c r="R31" t="n">
-        <v>6996600</v>
+        <v>6996784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,6 +3825,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3843,48 +3856,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364485</v>
+        <v>131364466</v>
       </c>
       <c r="B32" t="n">
-        <v>91843</v>
+        <v>91832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626311</v>
+        <v>626481</v>
       </c>
       <c r="R32" t="n">
-        <v>6996750</v>
+        <v>6996600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3935,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3944,42 +3953,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364480</v>
+        <v>131364485</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>91843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3987,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626363</v>
+        <v>626311</v>
       </c>
       <c r="R33" t="n">
-        <v>6996784</v>
+        <v>6996750</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,17 +4029,13 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364498</v>
+        <v>131364476</v>
       </c>
       <c r="B36" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,26 +4272,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4299,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626471</v>
+        <v>626499</v>
       </c>
       <c r="R36" t="n">
-        <v>6996618</v>
+        <v>6996587</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4339,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4348,24 +4353,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4382,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364476</v>
+        <v>131364501</v>
       </c>
       <c r="B37" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,31 +4382,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,13 +4409,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626499</v>
+        <v>626458</v>
       </c>
       <c r="R37" t="n">
-        <v>6996587</v>
+        <v>6996478</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4465,7 +4449,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4474,8 +4458,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4492,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131364501</v>
+        <v>131364498</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,21 +4503,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,13 +4530,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626458</v>
+        <v>626471</v>
       </c>
       <c r="R38" t="n">
-        <v>6996478</v>
+        <v>6996618</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Lunglav växandes på gran bredvid ett större aspträd</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,34 +4624,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R39" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,42 +4729,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R40" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364500</v>
+        <v>131364482</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,34 +1312,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626487</v>
+        <v>626675</v>
       </c>
       <c r="R8" t="n">
-        <v>6996447</v>
+        <v>6996443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,7 +1384,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,7 +1411,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364482</v>
+        <v>131364479</v>
       </c>
       <c r="B9" t="n">
         <v>57902</v>
@@ -1446,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626675</v>
+        <v>626431</v>
       </c>
       <c r="R9" t="n">
-        <v>6996443</v>
+        <v>6996531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364479</v>
+        <v>131364500</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,42 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626431</v>
+        <v>626487</v>
       </c>
       <c r="R10" t="n">
-        <v>6996531</v>
+        <v>6996447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131364481</v>
+        <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626505</v>
+        <v>626533</v>
       </c>
       <c r="R11" t="n">
-        <v>6996563</v>
+        <v>6996415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131364489</v>
+        <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,16 +1739,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1766,7 +1761,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626533</v>
+        <v>626505</v>
       </c>
       <c r="R12" t="n">
-        <v>6996415</v>
+        <v>6996563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364509</v>
+        <v>131364496</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626514</v>
+        <v>626311</v>
       </c>
       <c r="R18" t="n">
-        <v>6996422</v>
+        <v>6996692</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,11 +2442,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,6 +2453,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2474,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131364506</v>
+        <v>131364509</v>
       </c>
       <c r="B19" t="n">
         <v>79264</v>
@@ -2503,19 +2513,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626636</v>
+        <v>626514</v>
       </c>
       <c r="R19" t="n">
-        <v>6996473</v>
+        <v>6996422</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,7 +2562,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Rikliga mängder garnlav inom 25m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,6 +2571,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2576,48 +2590,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131364492</v>
+        <v>131364506</v>
       </c>
       <c r="B20" t="n">
-        <v>92292</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626333</v>
+        <v>626636</v>
       </c>
       <c r="R20" t="n">
-        <v>6996777</v>
+        <v>6996473</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,13 +2663,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2677,32 +2692,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B21" t="n">
-        <v>80369</v>
+        <v>92292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R21" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,21 +2777,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131364480</v>
+        <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,42 +3757,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626363</v>
+        <v>626481</v>
       </c>
       <c r="R31" t="n">
-        <v>6996784</v>
+        <v>6996600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,11 +3817,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,45 +3843,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131364466</v>
+        <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91832</v>
+        <v>91843</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626481</v>
+        <v>626311</v>
       </c>
       <c r="R32" t="n">
-        <v>6996600</v>
+        <v>6996750</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,6 +3925,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3953,37 +3944,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131364485</v>
+        <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>91843</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3991,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626311</v>
+        <v>626363</v>
       </c>
       <c r="R33" t="n">
-        <v>6996750</v>
+        <v>6996784</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,13 +4025,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,42 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R39" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4729,34 +4726,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R40" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131364504</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131364505</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131364490</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>131364474</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>131364475</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>131364470</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131364482</v>
+        <v>131364500</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,42 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626675</v>
+        <v>626487</v>
       </c>
       <c r="R8" t="n">
-        <v>6996443</v>
+        <v>6996447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,7 +1376,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364479</v>
+        <v>131364482</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626431</v>
+        <v>626675</v>
       </c>
       <c r="R9" t="n">
-        <v>6996531</v>
+        <v>6996443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364500</v>
+        <v>131364479</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1524,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626487</v>
+        <v>626431</v>
       </c>
       <c r="R10" t="n">
-        <v>6996447</v>
+        <v>6996531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
         <v>131364489</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131364481</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131364487</v>
+        <v>131364507</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,42 +1849,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626322</v>
+        <v>626550</v>
       </c>
       <c r="R13" t="n">
-        <v>6996755</v>
+        <v>6996438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,6 +1909,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131364507</v>
+        <v>131364497</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>80371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,34 +1951,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626550</v>
+        <v>626310</v>
       </c>
       <c r="R14" t="n">
-        <v>6996438</v>
+        <v>6996671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Växande på tre aspträd i närområdet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2027,8 +2027,24 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2045,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131364497</v>
+        <v>131364487</v>
       </c>
       <c r="B15" t="n">
-        <v>80369</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,26 +2072,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2083,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626310</v>
+        <v>626322</v>
       </c>
       <c r="R15" t="n">
-        <v>6996671</v>
+        <v>6996755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,35 +2142,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växande på tre aspträd i närområdet</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>131364493</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>131364488</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>131364496</v>
       </c>
       <c r="B18" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>131364509</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>131364506</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>131364492</v>
       </c>
       <c r="B21" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364478</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>91859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,54 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626721</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996435</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,19 +2861,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364484</v>
+        <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>91853</v>
+        <v>80371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,34 +2901,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626475</v>
+        <v>626292</v>
       </c>
       <c r="R23" t="n">
-        <v>6996475</v>
+        <v>6996716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,14 +2966,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3017,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>80369</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,37 +3022,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R24" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,14 +3099,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3104,24 +3120,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3141,7 +3141,7 @@
         <v>131364477</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>131364472</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131364465</v>
+        <v>131364467</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626312</v>
+        <v>626684</v>
       </c>
       <c r="R27" t="n">
-        <v>6996651</v>
+        <v>6996454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
         <v>131364469</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131364467</v>
+        <v>131364465</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626684</v>
+        <v>626312</v>
       </c>
       <c r="R29" t="n">
-        <v>6996454</v>
+        <v>6996651</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
         <v>131364468</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>131364466</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>131364485</v>
       </c>
       <c r="B32" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>131364480</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>131364473</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131364471</v>
+        <v>131364501</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,37 +4175,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626744</v>
+        <v>626458</v>
       </c>
       <c r="R35" t="n">
-        <v>6996412</v>
+        <v>6996478</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4237,14 +4240,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4261,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131364476</v>
+        <v>131364471</v>
       </c>
       <c r="B36" t="n">
-        <v>57902</v>
+        <v>91838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4272,42 +4296,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626499</v>
+        <v>626744</v>
       </c>
       <c r="R36" t="n">
-        <v>6996587</v>
+        <v>6996412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4340,11 +4356,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131364501</v>
+        <v>131364476</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4382,26 +4393,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4409,13 +4425,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626458</v>
+        <v>626499</v>
       </c>
       <c r="R37" t="n">
-        <v>6996478</v>
+        <v>6996587</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4449,7 +4465,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Måttliga mängder garnlav inom område på ca 25m</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4458,24 +4474,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4495,7 +4495,7 @@
         <v>131364498</v>
       </c>
       <c r="B38" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,34 +4624,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R39" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,42 +4729,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R40" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>80371</v>
+        <v>92298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,21 +2453,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2692,32 +2677,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>92298</v>
+        <v>80371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364484</v>
+        <v>131364494</v>
       </c>
       <c r="B22" t="n">
-        <v>91859</v>
+        <v>80371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,34 +2804,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626475</v>
+        <v>626292</v>
       </c>
       <c r="R22" t="n">
-        <v>6996475</v>
+        <v>6996716</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,14 +2869,35 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2890,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364494</v>
+        <v>131364478</v>
       </c>
       <c r="B23" t="n">
-        <v>80371</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,37 +2925,54 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626292</v>
+        <v>626721</v>
       </c>
       <c r="R23" t="n">
-        <v>6996716</v>
+        <v>6996435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,14 +3002,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2977,24 +3023,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3011,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364478</v>
+        <v>131364484</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>91859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,54 +3052,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626721</v>
+        <v>626475</v>
       </c>
       <c r="R24" t="n">
-        <v>6996435</v>
+        <v>6996475</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,19 +3109,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131364486</v>
+        <v>131364508</v>
       </c>
       <c r="B39" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,42 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626505</v>
+        <v>626544</v>
       </c>
       <c r="R39" t="n">
-        <v>6996430</v>
+        <v>6996401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131364508</v>
+        <v>131364486</v>
       </c>
       <c r="B40" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4729,34 +4726,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626544</v>
+        <v>626505</v>
       </c>
       <c r="R40" t="n">
-        <v>6996401</v>
+        <v>6996430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B18" t="n">
-        <v>92298</v>
+        <v>80371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R18" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2453,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2677,32 +2692,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B21" t="n">
-        <v>80371</v>
+        <v>92298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R21" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,21 +2777,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -1403,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131364482</v>
+        <v>131364479</v>
       </c>
       <c r="B9" t="n">
         <v>57904</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626675</v>
+        <v>626431</v>
       </c>
       <c r="R9" t="n">
-        <v>6996443</v>
+        <v>6996531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131364479</v>
+        <v>131364482</v>
       </c>
       <c r="B10" t="n">
         <v>57904</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626431</v>
+        <v>626675</v>
       </c>
       <c r="R10" t="n">
-        <v>6996531</v>
+        <v>6996443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131364496</v>
+        <v>131364492</v>
       </c>
       <c r="B18" t="n">
-        <v>80371</v>
+        <v>92298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626311</v>
+        <v>626333</v>
       </c>
       <c r="R18" t="n">
-        <v>6996692</v>
+        <v>6996777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,21 +2453,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2692,32 +2677,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131364492</v>
+        <v>131364496</v>
       </c>
       <c r="B21" t="n">
-        <v>92298</v>
+        <v>80371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626333</v>
+        <v>626311</v>
       </c>
       <c r="R21" t="n">
-        <v>6996777</v>
+        <v>6996692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,6 +2762,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131364494</v>
+        <v>131364484</v>
       </c>
       <c r="B22" t="n">
-        <v>80371</v>
+        <v>91859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,37 +2804,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626292</v>
+        <v>626475</v>
       </c>
       <c r="R22" t="n">
-        <v>6996716</v>
+        <v>6996475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,35 +2866,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt på asp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2914,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131364478</v>
+        <v>131364494</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>80371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,54 +2901,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626721</v>
+        <v>626292</v>
       </c>
       <c r="R23" t="n">
-        <v>6996435</v>
+        <v>6996716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,19 +2961,14 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,8 +2977,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3041,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131364484</v>
+        <v>131364478</v>
       </c>
       <c r="B24" t="n">
-        <v>91859</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,34 +3022,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hällsjö, Dal, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626475</v>
+        <v>626721</v>
       </c>
       <c r="R24" t="n">
-        <v>6996475</v>
+        <v>6996435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,9 +3099,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4818,6 +4818,108 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131364483</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hällsjö, Dal, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626707</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6996447</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bo?</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4818,108 +4818,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>131364483</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57948</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Hällsjö, Dal, Ång</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>626707</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6996447</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Dal</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Bo?</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4014-2026 artfynd.xlsx
+++ b/artfynd/A 4014-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364464</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364465</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364466</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364467</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364468</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364469</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364470</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364471</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364485</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364492</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364484</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364500</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2067,6 +2137,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364501</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364504</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2271,6 +2351,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364505</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2475,6 +2565,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364507</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2577,6 +2672,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2683,6 +2783,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364509</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2804,6 +2909,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364494</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2920,6 +3030,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364496</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364497</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3162,6 +3282,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364498</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3267,6 +3392,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364486</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364487</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3477,6 +3612,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364488</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3582,6 +3722,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364489</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3687,6 +3832,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364490</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3792,6 +3942,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364491</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3902,6 +4057,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364472</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4012,6 +4172,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364473</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4122,6 +4287,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364474</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4232,6 +4402,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364475</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4342,6 +4517,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364476</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4452,6 +4632,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364477</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4579,6 +4764,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364478</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4689,6 +4879,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364479</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4799,6 +4994,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364480</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4909,6 +5109,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364481</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5019,8 +5224,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131364482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>